--- a/docs/sprint2质量门禁与抗性报告/Sprint2质量门禁完成报告.xlsx
+++ b/docs/sprint2质量门禁与抗性报告/Sprint2质量门禁完成报告.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12790"/>
+    <workbookView windowWidth="25600" windowHeight="12790" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="门禁汇总" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="179">
   <si>
     <t>质量门禁完成报告</t>
   </si>
@@ -298,7 +298,7 @@
     <t>calculate_check_in_status</t>
   </si>
   <si>
-    <t>黄均</t>
+    <t>黄钧</t>
   </si>
   <si>
     <t>backend/tests/unit/modules/test_attendance_rules_unit.py</t>
@@ -610,9 +610,6 @@
     <t>C1</t>
   </si>
   <si>
-    <t>黄钧</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -2563,6 +2560,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF37352F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>根据现有代码结构整理核心测试范围，并将考勤、权限、</t>
     </r>
     <r>
@@ -2730,6 +2733,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF37352F"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
       <t>AI</t>
     </r>
     <r>
@@ -2798,6 +2807,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF37352F"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">`origin` </t>
     </r>
     <r>
@@ -2956,6 +2971,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF37352F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>对模块名、路径、权限码等字符串判断时，应按领域边界而非简单前缀判断，避免误伤合法输入。单元测试应优先依赖纯函数、</t>
     </r>
     <r>
@@ -2985,6 +3006,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF37352F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>建议不能替代团队优先级决策；未指出交叉</t>
     </r>
     <r>
@@ -3044,6 +3071,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF37352F"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
       <t>candidate_id/application_id</t>
     </r>
     <r>
@@ -3141,7 +3174,69 @@
     <t>门禁G4：性能检查记录</t>
   </si>
   <si>
-    <t>填写说明：列出至少3个关键页面和3个关键API，记录响应时间。首页要测首次加载和重复访问两种场景。</t>
+    <r>
+      <t>填写说明：列出至少</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF8C8A84"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF8C8A84"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个关键页面和</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF8C8A84"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF8C8A84"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个关键</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF8C8A84"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>API</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF8C8A84"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，记录响应时间。首页要测首次加载和重复访问两种场景。</t>
+    </r>
   </si>
   <si>
     <t>测试对象（页面/API）</t>
@@ -3207,6 +3302,15 @@
       </rPr>
       <t>/api/v1/attendance/today</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF37352F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（考勤页）</t>
+    </r>
   </si>
   <si>
     <t>http://localhost:8000/api/v1/attendance/today</t>
@@ -3239,6 +3343,15 @@
       </rPr>
       <t>/api/v1/audit/logs</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF37352F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（日志审核页）</t>
+    </r>
   </si>
   <si>
     <t>http://localhost:8000/api/v1/audit/logs</t>
@@ -3266,11 +3379,20 @@
         <rFont val="Noto Sans CJK SC"/>
         <charset val="134"/>
       </rPr>
-      <t>/api/v1/auth/me</t>
-    </r>
-  </si>
-  <si>
-    <t>http://localhost:8000/api/v1/auth/me</t>
+      <t>/api/v1/recruitment/candidates</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF37352F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（候选人池页）</t>
+    </r>
+  </si>
+  <si>
+    <t>http://localhost:8000/api/v1/recruitment/candidates</t>
   </si>
 </sst>
 </file>
@@ -3283,7 +3405,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3302,7 +3424,7 @@
       <i/>
       <sz val="9"/>
       <color rgb="FF8C8A84"/>
-      <name val="Noto Sans CJK SC"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3318,6 +3440,21 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF8C8A84"/>
+      <name val="Noto Sans CJK SC"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -3377,14 +3514,6 @@
       <color rgb="FF37352F"/>
       <name val="Noto Sans CJK SC"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -3872,134 +4001,134 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4028,19 +4157,25 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4052,43 +4187,43 @@
     <xf numFmtId="58" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="31" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4472,44 +4607,44 @@
   </cols>
   <sheetData>
     <row r="2" ht="36" customHeight="1" spans="2:7">
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="25" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="2:7">
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="27">
         <v>15</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="2:7">
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="27" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="2:7">
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="28" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="2:7">
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="29">
         <v>46218</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="2:7">
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="30" t="s">
         <v>7</v>
       </c>
     </row>
@@ -4546,10 +4681,10 @@
       <c r="E11" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="29" t="s">
+      <c r="F11" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="14" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4563,10 +4698,10 @@
       <c r="D12" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="30" t="s">
+      <c r="F12" s="32" t="s">
         <v>18</v>
       </c>
       <c r="G12" s="8" t="s">
@@ -4586,7 +4721,7 @@
       <c r="E13" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="29" t="s">
+      <c r="F13" s="31" t="s">
         <v>18</v>
       </c>
       <c r="G13" s="5" t="s">
@@ -4603,10 +4738,10 @@
       <c r="D14" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="F14" s="30" t="s">
+      <c r="F14" s="32" t="s">
         <v>18</v>
       </c>
       <c r="G14" s="8" t="s">
@@ -4626,7 +4761,7 @@
       <c r="E15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="29" t="s">
+      <c r="F15" s="31" t="s">
         <v>18</v>
       </c>
       <c r="G15" s="5" t="s">
@@ -4643,10 +4778,10 @@
       <c r="D16" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="F16" s="30" t="s">
+      <c r="F16" s="32" t="s">
         <v>18</v>
       </c>
       <c r="G16" s="8" t="s">
@@ -4654,10 +4789,10 @@
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="2:5">
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="32" t="str">
+      <c r="E18" s="34" t="str">
         <f>IF(COUNTIF(F11:F16,"通过")=6,"全部通过，可进入AI抗性挑战",IF(COUNTIF(F11:F16,"未通过")&gt;0,"有未通过项，需修复后重提交","部分通过，请补充未完成项"))</f>
         <v>全部通过，可进入AI抗性挑战</v>
       </c>
@@ -4715,7 +4850,7 @@
       </c>
     </row>
     <row r="3" ht="20.15" customHeight="1" spans="2:8">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="11" t="s">
         <v>47</v>
       </c>
     </row>
@@ -4743,7 +4878,7 @@
       </c>
     </row>
     <row r="5" ht="50.15" customHeight="1" spans="2:8">
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="13" t="s">
         <v>53</v>
       </c>
       <c r="C5" t="s">
@@ -4752,7 +4887,7 @@
       <c r="D5" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="14" t="s">
         <v>56</v>
       </c>
       <c r="F5" s="5" t="s">
@@ -4766,19 +4901,19 @@
       </c>
     </row>
     <row r="6" ht="50.15" customHeight="1" spans="2:8">
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="15" t="s">
         <v>60</v>
       </c>
       <c r="C6" t="s">
         <v>61</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="21" t="s">
         <v>57</v>
       </c>
       <c r="G6" t="s">
@@ -4789,19 +4924,19 @@
       </c>
     </row>
     <row r="7" ht="50.15" customHeight="1" spans="2:8">
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="13" t="s">
         <v>63</v>
       </c>
       <c r="C7" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="21" t="s">
         <v>57</v>
       </c>
       <c r="G7" t="s">
@@ -4812,19 +4947,19 @@
       </c>
     </row>
     <row r="8" ht="50.15" customHeight="1" spans="2:8">
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="15" t="s">
         <v>68</v>
       </c>
       <c r="C8" t="s">
         <v>69</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="21" t="s">
         <v>71</v>
       </c>
       <c r="G8" t="s">
@@ -4835,19 +4970,19 @@
       </c>
     </row>
     <row r="9" ht="50.15" customHeight="1" spans="2:8">
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="13" t="s">
         <v>73</v>
       </c>
       <c r="C9" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="21" t="s">
         <v>71</v>
       </c>
       <c r="G9" t="s">
@@ -4858,19 +4993,19 @@
       </c>
     </row>
     <row r="10" ht="68.5" customHeight="1" spans="2:8">
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="22" t="s">
         <v>77</v>
       </c>
       <c r="C10" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="21" t="s">
         <v>80</v>
       </c>
       <c r="G10" t="s">
@@ -4881,19 +5016,19 @@
       </c>
     </row>
     <row r="11" ht="69" customHeight="1" spans="2:8">
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="23" t="s">
         <v>82</v>
       </c>
       <c r="C11" t="s">
         <v>83</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="21" t="s">
         <v>80</v>
       </c>
       <c r="G11" t="s">
@@ -4904,19 +5039,19 @@
       </c>
     </row>
     <row r="12" ht="92" customHeight="1" spans="2:8">
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="22" t="s">
         <v>87</v>
       </c>
       <c r="C12" t="s">
         <v>88</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="21" t="s">
         <v>90</v>
       </c>
       <c r="G12" t="s">
@@ -4956,7 +5091,7 @@
       </c>
     </row>
     <row r="3" ht="20.15" customHeight="1" spans="2:9">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="11" t="s">
         <v>93</v>
       </c>
     </row>
@@ -4987,17 +5122,17 @@
       </c>
     </row>
     <row r="5" ht="117" customHeight="1" spans="2:9">
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="14" t="s">
         <v>102</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>103</v>
       </c>
       <c r="F5" s="5">
         <v>2</v>
@@ -5005,25 +5140,25 @@
       <c r="G5" s="5">
         <v>2</v>
       </c>
-      <c r="H5" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="I5" s="16">
+      <c r="H5" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="I5" s="18">
         <v>46216</v>
       </c>
     </row>
     <row r="6" ht="129" customHeight="1" spans="2:9">
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" s="16" t="s">
         <v>105</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>106</v>
       </c>
       <c r="F6" s="8">
         <v>2</v>
@@ -5032,24 +5167,24 @@
         <v>2</v>
       </c>
       <c r="H6" t="s">
-        <v>107</v>
-      </c>
-      <c r="I6" s="17">
+        <v>106</v>
+      </c>
+      <c r="I6" s="19">
         <v>46216</v>
       </c>
     </row>
     <row r="7" ht="129" customHeight="1" spans="2:9">
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>109</v>
       </c>
       <c r="F7" s="5">
         <v>2</v>
@@ -5058,24 +5193,24 @@
         <v>2</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="I7" s="16">
+        <v>109</v>
+      </c>
+      <c r="I7" s="18">
         <v>46216</v>
       </c>
     </row>
     <row r="8" ht="136" customHeight="1" spans="2:9">
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>111</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>112</v>
       </c>
       <c r="F8" s="8">
         <v>1</v>
@@ -5083,25 +5218,25 @@
       <c r="G8" s="8">
         <v>1</v>
       </c>
-      <c r="H8" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="I8" s="16">
+      <c r="H8" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="I8" s="18">
         <v>46216</v>
       </c>
     </row>
     <row r="9" ht="143" customHeight="1" spans="2:9">
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" s="14" t="s">
         <v>114</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>115</v>
       </c>
       <c r="F9" s="5">
         <v>2</v>
@@ -5109,25 +5244,25 @@
       <c r="G9" s="5">
         <v>2</v>
       </c>
-      <c r="H9" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="I9" s="16">
+      <c r="H9" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="I9" s="18">
         <v>46217</v>
       </c>
     </row>
     <row r="10" ht="138" customHeight="1" spans="2:9">
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>117</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>118</v>
       </c>
       <c r="F10" s="8">
         <v>2</v>
@@ -5135,25 +5270,25 @@
       <c r="G10" s="8">
         <v>2</v>
       </c>
-      <c r="H10" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="I10" s="17">
+      <c r="H10" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="I10" s="19">
         <v>46217</v>
       </c>
     </row>
     <row r="11" ht="128" customHeight="1" spans="2:9">
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="14" t="s">
         <v>120</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="F11" s="5">
         <v>2</v>
@@ -5161,25 +5296,25 @@
       <c r="G11" s="5">
         <v>2</v>
       </c>
-      <c r="H11" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="I11" s="16">
+      <c r="H11" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I11" s="18">
         <v>46217</v>
       </c>
     </row>
     <row r="12" ht="73" customHeight="1" spans="2:9">
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="20" t="s">
         <v>123</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>124</v>
       </c>
       <c r="F12" s="8">
         <v>2</v>
@@ -5187,10 +5322,10 @@
       <c r="G12" s="8">
         <v>2</v>
       </c>
-      <c r="H12" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="I12" s="17">
+      <c r="H12" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="I12" s="19">
         <v>46217</v>
       </c>
     </row>
@@ -5217,12 +5352,12 @@
   <sheetData>
     <row r="2" ht="32.15" customHeight="1" spans="2:7">
       <c r="B2" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" ht="20.15" customHeight="1" spans="2:7">
-      <c r="B3" s="2" t="s">
-        <v>127</v>
+      <c r="B3" s="11" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="2:7">
@@ -5230,104 +5365,104 @@
         <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="G4" s="12" t="s">
         <v>131</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="5" ht="80.15" customHeight="1" spans="2:7">
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="G5" s="14" t="s">
         <v>136</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="6" ht="80.15" customHeight="1" spans="2:7">
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="C6" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" s="14" t="s">
+      <c r="E6" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="F6" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="G6" s="16" t="s">
         <v>141</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="7" ht="80.15" customHeight="1" spans="2:7">
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="D7" s="12" t="s">
+      <c r="E7" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="14" t="s">
         <v>146</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="8" ht="80.15" customHeight="1" spans="2:7">
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="C8" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="D8" s="8" t="s">
+      <c r="E8" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="F8" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="G8" s="8" t="s">
         <v>151</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="9" ht="80.15" customHeight="1" spans="2:7">
-      <c r="B9" s="11" t="s">
-        <v>153</v>
+      <c r="B9" s="13" t="s">
+        <v>152</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -5336,8 +5471,8 @@
       <c r="G9" s="5"/>
     </row>
     <row r="10" ht="80.15" customHeight="1" spans="2:7">
-      <c r="B10" s="13" t="s">
-        <v>154</v>
+      <c r="B10" s="15" t="s">
+        <v>153</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -5371,12 +5506,12 @@
   <sheetData>
     <row r="2" ht="32.15" customHeight="1" spans="2:7">
       <c r="B2" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" ht="20.15" customHeight="1" spans="2:7">
       <c r="B3" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="2:7">
@@ -5384,119 +5519,119 @@
         <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="5" spans="2:7">
       <c r="B5" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>163</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>164</v>
       </c>
       <c r="E5" s="4">
         <v>910</v>
       </c>
       <c r="F5" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>165</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="6" spans="2:7">
       <c r="B6" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>168</v>
-      </c>
       <c r="D6" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E6" s="7">
         <v>870</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G6" s="8" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="7" ht="39" spans="2:7">
+      <c r="B7" s="4" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="7" ht="28" spans="2:7">
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>171</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>172</v>
       </c>
       <c r="E7" s="4">
         <v>54</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" ht="28" spans="2:7">
       <c r="B8" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="D8" s="9" t="s">
         <v>175</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>176</v>
       </c>
       <c r="E8" s="7">
         <v>43</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
-    <row r="9" ht="28" spans="2:7">
+    <row r="9" ht="38.5" spans="2:7">
       <c r="B9" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>179</v>
-      </c>
       <c r="E9" s="4">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -5522,7 +5657,7 @@
     <hyperlink ref="D5" r:id="rId2" display="http://localhost:5173/login"/>
     <hyperlink ref="D6" r:id="rId2" display="http://localhost:5173/login"/>
     <hyperlink ref="D8" r:id="rId3" display="http://localhost:8000/api/v1/audit/logs"/>
-    <hyperlink ref="D9" r:id="rId4" display="http://localhost:8000/api/v1/auth/me"/>
+    <hyperlink ref="D9" r:id="rId4" display="http://localhost:8000/api/v1/recruitment/candidates" tooltip="http://localhost:8000/api/v1/recruitment/candidates"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/docs/sprint2质量门禁与抗性报告/Sprint2质量门禁完成报告.xlsx
+++ b/docs/sprint2质量门禁与抗性报告/Sprint2质量门禁完成报告.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="185">
   <si>
     <t>质量门禁完成报告</t>
   </si>
@@ -3174,64 +3174,71 @@
     <t>门禁G4：性能检查记录</t>
   </si>
   <si>
-    <r>
-      <t>填写说明：列出至少</t>
-    </r>
     <r>
       <rPr>
         <i/>
         <sz val="9"/>
         <color rgb="FF8C8A84"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3</t>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>填写说明：列出至少</t>
     </r>
     <r>
       <rPr>
         <i/>
         <sz val="9"/>
         <color rgb="FF8C8A84"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>个关键页面和</t>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
     </r>
     <r>
       <rPr>
         <i/>
         <sz val="9"/>
         <color rgb="FF8C8A84"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3</t>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个关键页面和</t>
     </r>
     <r>
       <rPr>
         <i/>
         <sz val="9"/>
         <color rgb="FF8C8A84"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>个关键</t>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
     </r>
     <r>
       <rPr>
         <i/>
         <sz val="9"/>
         <color rgb="FF8C8A84"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>API</t>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个关键</t>
     </r>
     <r>
       <rPr>
         <i/>
         <sz val="9"/>
         <color rgb="FF8C8A84"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>API</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF8C8A84"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
@@ -3302,15 +3309,6 @@
       </rPr>
       <t>/api/v1/attendance/today</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF37352F"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（考勤页）</t>
-    </r>
   </si>
   <si>
     <t>http://localhost:8000/api/v1/attendance/today</t>
@@ -3343,15 +3341,6 @@
       </rPr>
       <t>/api/v1/audit/logs</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF37352F"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（日志审核页）</t>
-    </r>
   </si>
   <si>
     <t>http://localhost:8000/api/v1/audit/logs</t>
@@ -3381,18 +3370,27 @@
       </rPr>
       <t>/api/v1/recruitment/candidates</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF37352F"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（候选人池页）</t>
-    </r>
   </si>
   <si>
     <t>http://localhost:8000/api/v1/recruitment/candidates</t>
+  </si>
+  <si>
+    <t>P6</t>
+  </si>
+  <si>
+    <t>考勤页</t>
+  </si>
+  <si>
+    <t>P7</t>
+  </si>
+  <si>
+    <t>日志审核页</t>
+  </si>
+  <si>
+    <t>P8</t>
+  </si>
+  <si>
+    <t>候选人池页</t>
   </si>
 </sst>
 </file>
@@ -3450,16 +3448,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF37352F"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF8C8A84"/>
       <name val="Noto Sans CJK SC"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF37352F"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -4160,23 +4158,23 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4195,7 +4193,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4207,17 +4205,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="31" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4684,7 +4682,7 @@
       <c r="F11" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="11" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4738,7 +4736,7 @@
       <c r="D14" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="12" t="s">
         <v>33</v>
       </c>
       <c r="F14" s="32" t="s">
@@ -4778,7 +4776,7 @@
       <c r="D16" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="12" t="s">
         <v>43</v>
       </c>
       <c r="F16" s="32" t="s">
@@ -4850,7 +4848,7 @@
       </c>
     </row>
     <row r="3" ht="20.15" customHeight="1" spans="2:8">
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="13" t="s">
         <v>47</v>
       </c>
     </row>
@@ -4878,7 +4876,7 @@
       </c>
     </row>
     <row r="5" ht="50.15" customHeight="1" spans="2:8">
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="15" t="s">
         <v>53</v>
       </c>
       <c r="C5" t="s">
@@ -4887,7 +4885,7 @@
       <c r="D5" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="11" t="s">
         <v>56</v>
       </c>
       <c r="F5" s="5" t="s">
@@ -4901,7 +4899,7 @@
       </c>
     </row>
     <row r="6" ht="50.15" customHeight="1" spans="2:8">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="16" t="s">
         <v>60</v>
       </c>
       <c r="C6" t="s">
@@ -4910,7 +4908,7 @@
       <c r="D6" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="11" t="s">
         <v>56</v>
       </c>
       <c r="F6" s="21" t="s">
@@ -4924,7 +4922,7 @@
       </c>
     </row>
     <row r="7" ht="50.15" customHeight="1" spans="2:8">
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="15" t="s">
         <v>63</v>
       </c>
       <c r="C7" t="s">
@@ -4933,7 +4931,7 @@
       <c r="D7" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="11" t="s">
         <v>66</v>
       </c>
       <c r="F7" s="21" t="s">
@@ -4947,7 +4945,7 @@
       </c>
     </row>
     <row r="8" ht="50.15" customHeight="1" spans="2:8">
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="16" t="s">
         <v>68</v>
       </c>
       <c r="C8" t="s">
@@ -4956,7 +4954,7 @@
       <c r="D8" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="11" t="s">
         <v>66</v>
       </c>
       <c r="F8" s="21" t="s">
@@ -4970,7 +4968,7 @@
       </c>
     </row>
     <row r="9" ht="50.15" customHeight="1" spans="2:8">
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="15" t="s">
         <v>73</v>
       </c>
       <c r="C9" t="s">
@@ -4979,7 +4977,7 @@
       <c r="D9" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="11" t="s">
         <v>75</v>
       </c>
       <c r="F9" s="21" t="s">
@@ -5002,7 +5000,7 @@
       <c r="D10" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="F10" s="21" t="s">
@@ -5091,7 +5089,7 @@
       </c>
     </row>
     <row r="3" ht="20.15" customHeight="1" spans="2:9">
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="13" t="s">
         <v>93</v>
       </c>
     </row>
@@ -5122,7 +5120,7 @@
       </c>
     </row>
     <row r="5" ht="117" customHeight="1" spans="2:9">
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="15" t="s">
         <v>101</v>
       </c>
       <c r="C5" s="17" t="s">
@@ -5131,7 +5129,7 @@
       <c r="D5" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="11" t="s">
         <v>102</v>
       </c>
       <c r="F5" s="5">
@@ -5140,7 +5138,7 @@
       <c r="G5" s="5">
         <v>2</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="11" t="s">
         <v>103</v>
       </c>
       <c r="I5" s="18">
@@ -5148,7 +5146,7 @@
       </c>
     </row>
     <row r="6" ht="129" customHeight="1" spans="2:9">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="16" t="s">
         <v>104</v>
       </c>
       <c r="C6" s="17" t="s">
@@ -5157,7 +5155,7 @@
       <c r="D6" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="12" t="s">
         <v>105</v>
       </c>
       <c r="F6" s="8">
@@ -5174,13 +5172,13 @@
       </c>
     </row>
     <row r="7" ht="129" customHeight="1" spans="2:9">
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="11" t="s">
         <v>56</v>
       </c>
       <c r="E7" s="5" t="s">
@@ -5200,13 +5198,13 @@
       </c>
     </row>
     <row r="8" ht="136" customHeight="1" spans="2:9">
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="11" t="s">
         <v>56</v>
       </c>
       <c r="E8" s="8" t="s">
@@ -5218,7 +5216,7 @@
       <c r="G8" s="8">
         <v>1</v>
       </c>
-      <c r="H8" s="16" t="s">
+      <c r="H8" s="12" t="s">
         <v>112</v>
       </c>
       <c r="I8" s="18">
@@ -5226,16 +5224,16 @@
       </c>
     </row>
     <row r="9" ht="143" customHeight="1" spans="2:9">
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="11" t="s">
         <v>114</v>
       </c>
       <c r="F9" s="5">
@@ -5244,7 +5242,7 @@
       <c r="G9" s="5">
         <v>2</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="H9" s="11" t="s">
         <v>115</v>
       </c>
       <c r="I9" s="18">
@@ -5252,13 +5250,13 @@
       </c>
     </row>
     <row r="10" ht="138" customHeight="1" spans="2:9">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="11" t="s">
         <v>66</v>
       </c>
       <c r="E10" s="8" t="s">
@@ -5270,7 +5268,7 @@
       <c r="G10" s="8">
         <v>2</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="H10" s="12" t="s">
         <v>118</v>
       </c>
       <c r="I10" s="19">
@@ -5278,16 +5276,16 @@
       </c>
     </row>
     <row r="11" ht="128" customHeight="1" spans="2:9">
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="11" t="s">
         <v>120</v>
       </c>
       <c r="F11" s="5">
@@ -5296,7 +5294,7 @@
       <c r="G11" s="5">
         <v>2</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H11" s="11" t="s">
         <v>121</v>
       </c>
       <c r="I11" s="18">
@@ -5304,13 +5302,13 @@
       </c>
     </row>
     <row r="12" ht="73" customHeight="1" spans="2:9">
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="11" t="s">
         <v>75</v>
       </c>
       <c r="E12" s="20" t="s">
@@ -5322,7 +5320,7 @@
       <c r="G12" s="8">
         <v>2</v>
       </c>
-      <c r="H12" s="16" t="s">
+      <c r="H12" s="12" t="s">
         <v>124</v>
       </c>
       <c r="I12" s="19">
@@ -5356,7 +5354,7 @@
       </c>
     </row>
     <row r="3" ht="20.15" customHeight="1" spans="2:7">
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="13" t="s">
         <v>126</v>
       </c>
     </row>
@@ -5373,18 +5371,18 @@
       <c r="E4" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="14" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="5" ht="80.15" customHeight="1" spans="2:7">
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="11" t="s">
         <v>56</v>
       </c>
       <c r="D5" s="5" t="s">
@@ -5393,21 +5391,21 @@
       <c r="E5" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="11" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="6" ht="80.15" customHeight="1" spans="2:7">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="12" t="s">
         <v>138</v>
       </c>
       <c r="E6" s="8" t="s">
@@ -5416,18 +5414,18 @@
       <c r="F6" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="12" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="7" ht="80.15" customHeight="1" spans="2:7">
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="11" t="s">
         <v>143</v>
       </c>
       <c r="E7" s="5" t="s">
@@ -5436,21 +5434,21 @@
       <c r="F7" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="11" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="8" ht="80.15" customHeight="1" spans="2:7">
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="12" t="s">
         <v>75</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="12" t="s">
         <v>149</v>
       </c>
       <c r="F8" s="8" t="s">
@@ -5461,7 +5459,7 @@
       </c>
     </row>
     <row r="9" ht="80.15" customHeight="1" spans="2:7">
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="15" t="s">
         <v>152</v>
       </c>
       <c r="C9" s="5"/>
@@ -5471,7 +5469,7 @@
       <c r="G9" s="5"/>
     </row>
     <row r="10" ht="80.15" customHeight="1" spans="2:7">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="16" t="s">
         <v>153</v>
       </c>
       <c r="C10" s="8"/>
@@ -5493,7 +5491,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:G9"/>
+  <dimension ref="B2:G12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -5574,7 +5572,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="7" ht="39" spans="2:7">
+    <row r="7" ht="28" spans="2:7">
       <c r="B7" s="4" t="s">
         <v>169</v>
       </c>
@@ -5614,7 +5612,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="9" ht="38.5" spans="2:7">
+    <row r="9" ht="28" spans="2:7">
       <c r="B9" s="4" t="s">
         <v>176</v>
       </c>
@@ -5631,6 +5629,66 @@
         <v>164</v>
       </c>
       <c r="G9" s="5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="10" ht="28" spans="2:7">
+      <c r="B10" t="s">
+        <v>179</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="E10" s="4">
+        <v>54</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="11" ht="28" spans="2:7">
+      <c r="B11" t="s">
+        <v>181</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="E11" s="7">
+        <v>43</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="12" ht="28" spans="2:7">
+      <c r="B12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="E12" s="4">
+        <v>42</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>172</v>
       </c>
     </row>
@@ -5640,15 +5698,23 @@
     <mergeCell ref="B3:F3"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F9">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+      <formula>"达标"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+      <formula>"未达标"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F10:F12">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"未达标"</formula>
+    </cfRule>
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"达标"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"未达标"</formula>
-    </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="F5:F9">
+    <dataValidation type="list" allowBlank="1" sqref="F5:F9 F10:F12">
       <formula1>"达标,未达标"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5658,6 +5724,9 @@
     <hyperlink ref="D6" r:id="rId2" display="http://localhost:5173/login"/>
     <hyperlink ref="D8" r:id="rId3" display="http://localhost:8000/api/v1/audit/logs"/>
     <hyperlink ref="D9" r:id="rId4" display="http://localhost:8000/api/v1/recruitment/candidates" tooltip="http://localhost:8000/api/v1/recruitment/candidates"/>
+    <hyperlink ref="D10" r:id="rId1" display="http://localhost:8000/api/v1/attendance/today"/>
+    <hyperlink ref="D11" r:id="rId3" display="http://localhost:8000/api/v1/audit/logs"/>
+    <hyperlink ref="D12" r:id="rId4" display="http://localhost:8000/api/v1/recruitment/candidates" tooltip="http://localhost:8000/api/v1/recruitment/candidates"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
